--- a/reports/pdf_weekly_20260731.xlsx
+++ b/reports/pdf_weekly_20260731.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,438억   ·   현금 299억(8.8%)      주말 2026-07-31  vs  주초 2026-07-27      매수 9종목  /  매도 8종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 3,286억   ·   현금 300억(8.8%)      주말 2026-07-31  vs  주초 2026-07-27      매수 9종목  /  매도 8종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -670,7 +670,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>380259360</v>
+        <v>381781920</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -691,7 +691,7 @@
         <v>-171</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-10488900600</v>
+        <v>-10530898200</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>46</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>944354700</v>
+        <v>948135900</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>-59</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2876320800</v>
+        <v>-2887837600</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -758,7 +758,7 @@
         <v>31</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1336312350</v>
+        <v>1341662950</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>-36</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-663176160</v>
+        <v>-665831520</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>921327750</v>
+        <v>925016750</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         <v>-35</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-458391150</v>
+        <v>-460226550</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         <v>26</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>642856500</v>
+        <v>645430500</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>-31</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-763385850</v>
+        <v>-766442450</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>22</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>467032500</v>
+        <v>468902500</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>-27</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-2414083500</v>
+        <v>-2423749500</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>19</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>629220150</v>
+        <v>631739550</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>-19</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-698500800</v>
+        <v>-701297600</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>14</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>892306800</v>
+        <v>895879600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>-6</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2235762000</v>
+        <v>-2244714000</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>5</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>791208000</v>
+        <v>794376000</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1043,7 +1043,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,104억   ·   현금 26억(0.9%)      주말 2026-07-31  vs  주초 2026-07-27      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,004억   ·   현금 26억(0.9%)      주말 2026-07-31  vs  주초 2026-07-27      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1067,7 +1067,7 @@
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,929억   ·   현금 65억(3.5%)      주말 2026-07-31  vs  주초 2026-07-27      매수 4종목  /  매도 3종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 1,812억   ·   현금 65억(3.5%)      주말 2026-07-31  vs  주초 2026-07-27      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B19" s="4" t="n"/>
@@ -1163,7 +1163,7 @@
         <v>26</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>308479080</v>
+        <v>307135920</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1184,7 +1184,7 @@
         <v>-110</v>
       </c>
       <c r="I22" s="15" t="n">
-        <v>-4653506000</v>
+        <v>-4633244000</v>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         <v>22</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>4236661000</v>
+        <v>4218214000</v>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>-20</v>
       </c>
       <c r="I23" s="15" t="n">
-        <v>-1378000000</v>
+        <v>-1372000000</v>
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
@@ -1251,7 +1251,7 @@
         <v>4</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>1027988000</v>
+        <v>1023512000</v>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>-3</v>
       </c>
       <c r="I24" s="15" t="n">
-        <v>-145930200</v>
+        <v>-145294800</v>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>3</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>61493250</v>
+        <v>61225500</v>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
     <row r="27" ht="19" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,829억   ·   현금 67억(3.7%)      주말 2026-07-31  vs  주초 2026-07-27      매수 4종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,799억   ·   현금 67억(3.7%)      주말 2026-07-31  vs  주초 2026-07-27      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B27" s="4" t="n"/>
@@ -1412,7 +1412,7 @@
         <v>238</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>4818643200</v>
+        <v>4847584000</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>-80</v>
       </c>
       <c r="I30" s="15" t="n">
-        <v>-5061600000</v>
+        <v>-5092000000</v>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>20</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>1861470000</v>
+        <v>1872650000</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>-68</v>
       </c>
       <c r="I31" s="15" t="n">
-        <v>-1763967600</v>
+        <v>-1774562000</v>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>11</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>167399100</v>
+        <v>168404500</v>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>-7</v>
       </c>
       <c r="I32" s="15" t="n">
-        <v>-3559437000</v>
+        <v>-3580815000</v>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>7</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>208624500</v>
+        <v>209877500</v>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
     <row r="35" ht="19" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 218억   ·   현금 14억(6.3%)      주말 2026-07-31  vs  주초 2026-07-27      매수 8종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 212억   ·   현금 14억(6.5%)      주말 2026-07-31  vs  주초 2026-07-27      매수 8종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B35" s="4" t="n"/>
@@ -1661,11 +1661,11 @@
         <v>62</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>12604600</v>
+        <v>12321880</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>0.45%→0.53%</t>
+          <t>0.46%→0.54%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>2.88%→0.00%</t>
+          <t>3.01%→0.00%</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
@@ -1705,11 +1705,11 @@
         <v>49</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>54891760</v>
+        <v>57870960</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>2.94%→3.30%</t>
+          <t>3.25%→3.64%</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -1726,11 +1726,11 @@
         <v>-145</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-35098700</v>
+        <v>-35319100</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>2.88%→2.81%</t>
+          <t>3.03%→2.96%</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
@@ -1749,11 +1749,11 @@
         <v>33</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>74111400</v>
+        <v>69973200</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>6.87%→7.43%</t>
+          <t>6.78%→7.36%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -1770,11 +1770,11 @@
         <v>-91</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-43778280</v>
+        <v>-44884840</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>1.03%→0.85%</t>
+          <t>1.10%→0.92%</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -1793,11 +1793,11 @@
         <v>28</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>50008000</v>
+        <v>47241600</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>2.28%→2.58%</t>
+          <t>2.25%→2.56%</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -1814,11 +1814,11 @@
         <v>-8</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-29579200</v>
+        <v>-27785600</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.64%→0.52%</t>
+          <t>0.63%→0.52%</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -1837,11 +1837,11 @@
         <v>15</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>65094000</v>
+        <v>57684000</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>3.34%→3.76%</t>
+          <t>3.10%→3.49%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -1858,7 +1858,7 @@
         <v>-7</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-44102800</v>
+        <v>-41442800</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -1881,11 +1881,11 @@
         <v>13</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>21291400</v>
+        <v>20846800</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>0.74%→0.86%</t>
+          <t>0.75%→0.88%</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -1902,11 +1902,11 @@
         <v>-6</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-128820000</v>
+        <v>-127452000</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.42%</t>
+          <t>2.04%→1.47%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -1925,11 +1925,11 @@
         <v>11</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>46732400</v>
+        <v>43304800</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>1.66%→1.93%</t>
+          <t>1.61%→1.87%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -1946,11 +1946,11 @@
         <v>-6</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-107388000</v>
+        <v>-103512000</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>1.97%→1.52%</t>
+          <t>1.99%→1.54%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -1969,11 +1969,11 @@
         <v>4</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>34929600</v>
+        <v>30825600</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>2.88%→3.14%</t>
+          <t>2.66%→2.90%</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -1990,7 +1990,7 @@
     <row r="47" ht="19" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 433억   ·   현금 24억(5.7%)      주말 2026-07-31  vs  주초 2026-07-27      매수 4종목  /  매도 4종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 418억   ·   현금 24억(5.7%)      주말 2026-07-31  vs  주초 2026-07-27      매수 4종목  /  매도 4종목</t>
         </is>
       </c>
       <c r="B47" s="4" t="n"/>
@@ -2086,7 +2086,7 @@
         <v>51</v>
       </c>
       <c r="C50" s="11" t="n">
-        <v>475167000</v>
+        <v>483806400</v>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>-607</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-735805400</v>
+        <v>-749183680</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2130,7 +2130,7 @@
         <v>10</v>
       </c>
       <c r="C51" s="11" t="n">
-        <v>132880000</v>
+        <v>135296000</v>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         <v>-518</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-418233200</v>
+        <v>-425837440</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2174,7 +2174,7 @@
         <v>9</v>
       </c>
       <c r="C52" s="11" t="n">
-        <v>222255000</v>
+        <v>226296000</v>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>-33</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-689700000</v>
+        <v>-702240000</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>4</v>
       </c>
       <c r="C53" s="11" t="n">
-        <v>671880000</v>
+        <v>684096000</v>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>-9</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-276705000</v>
+        <v>-281736000</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>

--- a/reports/pdf_weekly_20260731.xlsx
+++ b/reports/pdf_weekly_20260731.xlsx
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>지엔씨에너지  (신규)</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>1341662950</v>
+        <v>925016750</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.20%→0.64%</t>
+          <t>0.00%→0.30%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>15→46</t>
+          <t>0→31</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지  (신규)</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>925016750</v>
+        <v>1341662950</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.30%</t>
+          <t>0.20%→0.64%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>0→31</t>
+          <t>15→46</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">

--- a/reports/pdf_weekly_20260731.xlsx
+++ b/reports/pdf_weekly_20260731.xlsx
@@ -751,23 +751,23 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>지엔씨에너지  (신규)</t>
+          <t>하나머티리얼즈</t>
         </is>
       </c>
       <c r="B8" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>925016750</v>
+        <v>1341662950</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.30%</t>
+          <t>0.20%→0.64%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>0→31</t>
+          <t>15→46</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -795,23 +795,23 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
-          <t>하나머티리얼즈</t>
+          <t>지엔씨에너지  (신규)</t>
         </is>
       </c>
       <c r="B9" s="11" t="n">
         <v>31</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1341662950</v>
+        <v>925016750</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>0.20%→0.64%</t>
+          <t>0.00%→0.30%</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>15→46</t>
+          <t>0→31</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
